--- a/juice_heating_station.xlsx
+++ b/juice_heating_station.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,10 +49,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -89,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,16 +107,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <top style="medium">
-        <color rgb="001F4E78"/>
-      </top>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -160,22 +151,19 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -604,22 +592,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34.14" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -632,29 +614,17 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2 heaters | juice out 1,400,000 lb/hr @ 220.0 °F | steam = 167,323 lb/hr</t>
+          <t>2 heaters | juice out 1,400,000 lb/hr @ 220.0 °F | steam = 168,164 lb/hr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
     </row>
     <row r="4"/>
     <row r="5" ht="17" customHeight="1">
@@ -667,12 +637,6 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -684,12 +648,6 @@
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -830,13 +788,13 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>82938.05506917194</v>
+        <v>83779.43035673695</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>225.2010543089987</v>
+        <v>240.0335477178342</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -868,13 +826,13 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>82938.05506917194</v>
+        <v>83779.43035673695</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>225.2010543089987</v>
+        <v>240.0335477178342</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -899,223 +857,367 @@
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>HEATER PERFORMANCE</t>
+          <t>HEATER FLOWS</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="5" t="n"/>
       <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Heater</t>
-        </is>
-      </c>
+      <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Juice (lb/hr)</t>
+          <t>Primary Heaters</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>T in (°F)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>T out (°F)</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>LMTD (°F)</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Duty (BTU/hr)</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>U (BTU/hr·ft²·°F)</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Req Area (ft²)</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>Inst Area (ft²)</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>Steam (psia)</t>
-        </is>
-      </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>Steam (lb/hr)</t>
+          <t>Secondary Heaters</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Primary Heaters</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="n">
+          <t>Juice (lb/hr)</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
         <v>700000</v>
       </c>
-      <c r="C50" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>220</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>38.81724210383579</v>
-      </c>
-      <c r="F50" s="9" t="n">
-        <v>79761500</v>
-      </c>
-      <c r="G50" s="10" t="n">
-        <v>220</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>9339.980201515824</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K50" s="9" t="n">
-        <v>82938.05506917194</v>
+      <c r="C50" s="15" t="n">
+        <v>700000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
+          <t>Juice cp (BTU/lb·°F)</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>0.9115599999999999</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>0.9115599999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Juice ΔT (°F)</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Duty (BTU/hr)</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>79761500</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>79761500</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Req Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>5741.542607248358</v>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>4739.805136828332</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Inst Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Steam (lb/hr)</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>83779.43035673695</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>84384.70769476538</v>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>HEATER CONDITIONS</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Primary Heaters</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
           <t>Secondary Heaters</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n">
-        <v>700000</v>
-      </c>
-      <c r="C51" s="14" t="n">
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Steam Type</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>T in (°F)</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="n">
         <v>95</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="C61" s="16" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>T out (°F)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n">
         <v>220</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="C62" s="15" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>LMTD (°F)</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="n">
+        <v>63.14544670792339</v>
+      </c>
+      <c r="C63" s="16" t="n">
         <v>76.49096582267444</v>
       </c>
-      <c r="F51" s="13" t="n">
-        <v>79761500</v>
-      </c>
-      <c r="G51" s="14" t="n">
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>U (BTU/hr·ft²·°F)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
         <v>220</v>
       </c>
-      <c r="H51" s="13" t="n">
-        <v>4739.805136828332</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J51" s="14" t="n">
+      <c r="C64" s="15" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Steam (psia)</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C65" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="K51" s="13" t="n">
-        <v>84384.70769476538</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr"/>
-      <c r="C52" s="15" t="inlineStr"/>
-      <c r="D52" s="15" t="inlineStr"/>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="16" t="n">
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Total duty</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
         <v>159523000</v>
       </c>
-      <c r="G52" s="15" t="inlineStr"/>
-      <c r="H52" s="15" t="inlineStr"/>
-      <c r="I52" s="15" t="inlineStr"/>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="16" t="n">
-        <v>167322.7627639373</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Total steam</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="n">
+        <v>168164.1380515023</v>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Juice split between heaters</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>50% / 50%</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Hot juice out</t>
         </is>
       </c>
-      <c r="B54" s="19" t="n">
+      <c r="B69" s="18" t="n">
         <v>1400000</v>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>Hot juice temperature</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n">
+      <c r="B70" s="20" t="n">
         <v>220</v>
       </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CONDENSATE RETURN</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>Clean condensate (Exhaust steam heaters)</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="n">
+        <v>81052.71479792673</v>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>Dirty condensate (V1-V4 steam heaters)</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>81358.15751273844</v>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>Total condensate</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="n">
+        <v>162410.8723106652</v>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A58:E58"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="46" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1124,22 +1226,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34.14" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1152,29 +1248,17 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2 heaters | juice out 1,400,000 lb/hr @ 220.0 °F | steam = 165,876 lb/hr</t>
+          <t>2 heaters | juice out 1,400,000 lb/hr @ 220.0 °F | steam = 167,559 lb/hr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
     </row>
     <row r="4"/>
     <row r="5" ht="17" customHeight="1">
@@ -1187,12 +1271,6 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -1204,12 +1282,6 @@
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1299,13 +1371,13 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>165876.1101383439</v>
+        <v>167558.8607134739</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>225.2010543089987</v>
+        <v>240.0335477178342</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -1337,13 +1409,13 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>165876.1101383439</v>
+        <v>167558.8607134739</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>225.2010543089987</v>
+        <v>240.0335477178342</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -1368,211 +1440,355 @@
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HEATER PERFORMANCE</t>
+          <t>HEATER FLOWS</t>
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Heater</t>
-        </is>
-      </c>
+      <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Juice (lb/hr)</t>
+          <t>Primary Heaters</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>T in (°F)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>T out (°F)</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>LMTD (°F)</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Duty (BTU/hr)</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>U (BTU/hr·ft²·°F)</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Req Area (ft²)</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Inst Area (ft²)</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>Steam (psia)</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>Steam (lb/hr)</t>
+          <t>Secondary Heaters</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Primary Heaters</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="n">
+          <t>Juice (lb/hr)</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
         <v>1400000</v>
       </c>
-      <c r="C47" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>220</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>38.81724210383579</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>159523000</v>
-      </c>
-      <c r="G47" s="10" t="n">
-        <v>220</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>18679.96040303165</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <v>165876.1101383439</v>
+      <c r="C47" s="15" t="n">
+        <v>1400000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t>Juice cp (BTU/lb·°F)</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>0.9115599999999999</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>0.9115599999999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Juice ΔT (°F)</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Duty (BTU/hr)</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>159523000</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Req Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>11483.08521449672</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Inst Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Steam (lb/hr)</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n">
+        <v>167558.8607134739</v>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>HEATER CONDITIONS</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Primary Heaters</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
           <t>Secondary Heaters</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Steam Type</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>T in (°F)</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>T out (°F)</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>LMTD (°F)</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>63.14544670792339</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>30.30117089016107</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>U (BTU/hr·ft²·°F)</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Steam (psia)</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Total duty</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n">
+        <v>159523000</v>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Total steam</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n">
+        <v>167558.8607134739</v>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>Hot juice out</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="n">
         <v>1400000</v>
       </c>
-      <c r="C48" s="14" t="n">
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Hot juice temperature</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n">
         <v>220</v>
       </c>
-      <c r="D48" s="14" t="n">
-        <v>220</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>30.30117089016107</v>
-      </c>
-      <c r="F48" s="13" t="n">
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>CONDENSATE RETURN</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Clean condensate (Exhaust steam heaters)</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="14" t="n">
-        <v>220</v>
-      </c>
-      <c r="H48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J48" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr"/>
-      <c r="C49" s="15" t="inlineStr"/>
-      <c r="D49" s="15" t="inlineStr"/>
-      <c r="E49" s="15" t="inlineStr"/>
-      <c r="F49" s="16" t="n">
-        <v>159523000</v>
-      </c>
-      <c r="G49" s="15" t="inlineStr"/>
-      <c r="H49" s="15" t="inlineStr"/>
-      <c r="I49" s="15" t="inlineStr"/>
-      <c r="J49" s="15" t="inlineStr"/>
-      <c r="K49" s="16" t="n">
-        <v>165876.1101383439</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Hot juice out</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>Hot juice temperature</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="n">
-        <v>220</v>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>°F</t>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>Dirty condensate (V1-V4 steam heaters)</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="n">
+        <v>162716.3150254769</v>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Total condensate</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n">
+        <v>162716.3150254769</v>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A45:K45"/>
+  <mergeCells count="7">
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="43" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>